--- a/Data/2035/REPowerEU++/Input/Xlsx/Node.xlsx
+++ b/Data/2035/REPowerEU++/Input/Xlsx/Node.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C360"/>
+  <dimension ref="A1:C353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,4550 +547,4459 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>300778111.111352</v>
+        <v>50419611.111151</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>338763333.333604</v>
+        <v>52786555.555598</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>369569888.889184</v>
+        <v>52733777.77782</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>380894444.444749</v>
+        <v>54624777.777821</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>388909166.666978</v>
+        <v>59961166.666715</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>391276694.444758</v>
+        <v>60926750.000049</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>404111861.111434</v>
+        <v>71335472.222279</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>50419611.111151</v>
+        <v>2465522138.613083</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>52786555.555598</v>
+        <v>2724776847.50218</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>52733777.77782</v>
+        <v>3078172701.391351</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>54624777.777821</v>
+        <v>3210483574.169235</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>5</v>
       </c>
       <c r="C22" t="n">
-        <v>59961166.666715</v>
+        <v>3549711221.391728</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>6</v>
       </c>
       <c r="C23" t="n">
-        <v>60926750.000049</v>
+        <v>3596422945.558433</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>7</v>
       </c>
       <c r="C24" t="n">
-        <v>71335472.222279</v>
+        <v>3833773383.614178</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>2164744027.501731</v>
+        <v>7206020.739735</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>2386013514.168575</v>
+        <v>7885782.181668</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>2708602812.502167</v>
+        <v>10905124.180169</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>4</v>
       </c>
       <c r="C28" t="n">
-        <v>2829589129.724486</v>
+        <v>10607350.914561</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>3160802054.724751</v>
+        <v>11423683.60094</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>6</v>
       </c>
       <c r="C30" t="n">
-        <v>3205146251.113675</v>
+        <v>11222636.817559</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>7</v>
       </c>
       <c r="C31" t="n">
-        <v>3429661522.502744</v>
+        <v>13063143.105956</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES112</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>7206020.739735</v>
+        <v>7417847.478136</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES112</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>7885782.181668</v>
+        <v>8117591.050892</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES112</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>10905124.180169</v>
+        <v>11225689.020374</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES112</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>4</v>
       </c>
       <c r="C35" t="n">
-        <v>10607350.914561</v>
+        <v>10919162.471655</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES112</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>5</v>
       </c>
       <c r="C36" t="n">
-        <v>11423683.60094</v>
+        <v>11759491.90973</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES112</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>6</v>
       </c>
       <c r="C37" t="n">
-        <v>11222636.817559</v>
+        <v>11552535.195483</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES112</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>7</v>
       </c>
       <c r="C38" t="n">
-        <v>13063143.105956</v>
+        <v>13447144.637084</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ES112</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>7417847.478136</v>
+        <v>1754257.825053</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ES112</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>8117591.050892</v>
+        <v>1919741.227301</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ES112</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>3</v>
       </c>
       <c r="C41" t="n">
-        <v>11225689.020374</v>
+        <v>2654779.956537</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ES112</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>4</v>
       </c>
       <c r="C42" t="n">
-        <v>10919162.471655</v>
+        <v>2582289.035382</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ES112</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>5</v>
       </c>
       <c r="C43" t="n">
-        <v>11759491.90973</v>
+        <v>2781019.798816</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ES112</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>6</v>
       </c>
       <c r="C44" t="n">
-        <v>11552535.195483</v>
+        <v>2732076.296474</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ES112</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>7</v>
       </c>
       <c r="C45" t="n">
-        <v>13447144.637084</v>
+        <v>3180135.311997</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES114</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>1754257.825053</v>
+        <v>4569257.737304</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES114</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>2</v>
       </c>
       <c r="C47" t="n">
-        <v>1919741.227301</v>
+        <v>5000286.919742</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES114</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>3</v>
       </c>
       <c r="C48" t="n">
-        <v>2654779.956537</v>
+        <v>6914818.15501</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES114</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>4</v>
       </c>
       <c r="C49" t="n">
-        <v>2582289.035382</v>
+        <v>6726003.433685</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES114</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>5</v>
       </c>
       <c r="C50" t="n">
-        <v>2781019.798816</v>
+        <v>7243630.925774</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES114</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>6</v>
       </c>
       <c r="C51" t="n">
-        <v>2732076.296474</v>
+        <v>7116149.392803</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES114</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>7</v>
       </c>
       <c r="C52" t="n">
-        <v>3180135.311997</v>
+        <v>8283193.993776</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ES114</t>
+          <t>ES120</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>4569257.737304</v>
+        <v>12861457.826521</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ES114</t>
+          <t>ES120</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>2</v>
       </c>
       <c r="C54" t="n">
-        <v>5000286.919742</v>
+        <v>14074710.38758</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ES114</t>
+          <t>ES120</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>3</v>
       </c>
       <c r="C55" t="n">
-        <v>6914818.15501</v>
+        <v>19463695.679203</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ES114</t>
+          <t>ES120</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>4</v>
       </c>
       <c r="C56" t="n">
-        <v>6726003.433685</v>
+        <v>18932223.673251</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ES114</t>
+          <t>ES120</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>5</v>
       </c>
       <c r="C57" t="n">
-        <v>7243630.925774</v>
+        <v>20389231.472352</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ES114</t>
+          <t>ES120</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>6</v>
       </c>
       <c r="C58" t="n">
-        <v>7116149.392803</v>
+        <v>20030398.932313</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ES114</t>
+          <t>ES120</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>7</v>
       </c>
       <c r="C59" t="n">
-        <v>8283193.993776</v>
+        <v>23315373.381128</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ES120</t>
+          <t>ES130</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>1</v>
       </c>
       <c r="C60" t="n">
-        <v>12861457.826521</v>
+        <v>4497719.70055</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ES120</t>
+          <t>ES130</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>2</v>
       </c>
       <c r="C61" t="n">
-        <v>14074710.38758</v>
+        <v>4922000.526193</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ES120</t>
+          <t>ES130</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>3</v>
       </c>
       <c r="C62" t="n">
-        <v>19463695.679203</v>
+        <v>6806557.132376</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ES120</t>
+          <t>ES130</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>4</v>
       </c>
       <c r="C63" t="n">
-        <v>18932223.673251</v>
+        <v>6620698.56613</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ES120</t>
+          <t>ES130</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>5</v>
       </c>
       <c r="C64" t="n">
-        <v>20389231.472352</v>
+        <v>7130221.885357</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ES120</t>
+          <t>ES130</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>6</v>
       </c>
       <c r="C65" t="n">
-        <v>20030398.932313</v>
+        <v>7004736.251746</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ES120</t>
+          <t>ES130</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>7</v>
       </c>
       <c r="C66" t="n">
-        <v>23315373.381128</v>
+        <v>8153509.158637</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ES130</t>
+          <t>ES211</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>1</v>
       </c>
       <c r="C67" t="n">
-        <v>4497719.70055</v>
+        <v>3277458.412809</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ES130</t>
+          <t>ES211</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>2</v>
       </c>
       <c r="C68" t="n">
-        <v>4922000.526193</v>
+        <v>3586629.026804</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ES130</t>
+          <t>ES211</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>3</v>
       </c>
       <c r="C69" t="n">
-        <v>6806557.132376</v>
+        <v>4959892.88373</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ES130</t>
+          <t>ES211</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>4</v>
       </c>
       <c r="C70" t="n">
-        <v>6620698.56613</v>
+        <v>4824458.983423</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ES130</t>
+          <t>ES211</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>5</v>
       </c>
       <c r="C71" t="n">
-        <v>7130221.885357</v>
+        <v>5195745.235191</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ES130</t>
+          <t>ES211</t>
         </is>
       </c>
       <c r="B72" t="n">
         <v>6</v>
       </c>
       <c r="C72" t="n">
-        <v>7004736.251746</v>
+        <v>5104304.689104</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ES130</t>
+          <t>ES211</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>7</v>
       </c>
       <c r="C73" t="n">
-        <v>8153509.158637</v>
+        <v>5941407.861104</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ES211</t>
+          <t>ES212</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>3277458.412809</v>
+        <v>7594231.621619</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ES211</t>
+          <t>ES212</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>2</v>
       </c>
       <c r="C75" t="n">
-        <v>3586629.026804</v>
+        <v>8310613.939119</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ES211</t>
+          <t>ES212</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>3</v>
       </c>
       <c r="C76" t="n">
-        <v>4959892.88373</v>
+        <v>11492617.337342</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ES211</t>
+          <t>ES212</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>4</v>
       </c>
       <c r="C77" t="n">
-        <v>4824458.983423</v>
+        <v>11178802.094307</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ES211</t>
+          <t>ES212</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>5</v>
       </c>
       <c r="C78" t="n">
-        <v>5195745.235191</v>
+        <v>12039113.176466</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ES211</t>
+          <t>ES212</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>6</v>
       </c>
       <c r="C79" t="n">
-        <v>5104304.689104</v>
+        <v>11827235.373873</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ES211</t>
+          <t>ES212</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>7</v>
       </c>
       <c r="C80" t="n">
-        <v>5941407.861104</v>
+        <v>13766895.494202</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ES212</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>1</v>
       </c>
       <c r="C81" t="n">
-        <v>7594231.621619</v>
+        <v>8366226.832937</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ES212</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>2</v>
       </c>
       <c r="C82" t="n">
-        <v>8310613.939119</v>
+        <v>9155433.334124999</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ES212</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>3</v>
       </c>
       <c r="C83" t="n">
-        <v>11492617.337342</v>
+        <v>12660904.794454</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ES212</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>4</v>
       </c>
       <c r="C84" t="n">
-        <v>11178802.094307</v>
+        <v>12315188.514299</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ES212</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>5</v>
       </c>
       <c r="C85" t="n">
-        <v>12039113.176466</v>
+        <v>13262954.926867</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ES212</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>6</v>
       </c>
       <c r="C86" t="n">
-        <v>11827235.373873</v>
+        <v>13029538.585928</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ES212</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>7</v>
       </c>
       <c r="C87" t="n">
-        <v>13766895.494202</v>
+        <v>15166375.774206</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ES213</t>
+          <t>ES220</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>1</v>
       </c>
       <c r="C88" t="n">
-        <v>8366226.832937</v>
+        <v>6799407.519883</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ES213</t>
+          <t>ES220</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>2</v>
       </c>
       <c r="C89" t="n">
-        <v>9155433.334124999</v>
+        <v>7440812.149004</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ES213</t>
+          <t>ES220</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>3</v>
       </c>
       <c r="C90" t="n">
-        <v>12660904.794454</v>
+        <v>10289782.118866</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ES213</t>
+          <t>ES220</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>4</v>
       </c>
       <c r="C91" t="n">
-        <v>12315188.514299</v>
+        <v>10008811.267613</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ES213</t>
+          <t>ES220</t>
         </is>
       </c>
       <c r="B92" t="n">
         <v>5</v>
       </c>
       <c r="C92" t="n">
-        <v>13262954.926867</v>
+        <v>10779080.852862</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ES213</t>
+          <t>ES220</t>
         </is>
       </c>
       <c r="B93" t="n">
         <v>6</v>
       </c>
       <c r="C93" t="n">
-        <v>13029538.585928</v>
+        <v>10589378.51087</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ES213</t>
+          <t>ES220</t>
         </is>
       </c>
       <c r="B94" t="n">
         <v>7</v>
       </c>
       <c r="C94" t="n">
-        <v>15166375.774206</v>
+        <v>12326030.783977</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ES220</t>
+          <t>ES230</t>
         </is>
       </c>
       <c r="B95" t="n">
         <v>1</v>
       </c>
       <c r="C95" t="n">
-        <v>6799407.519883</v>
+        <v>2724366.315664</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ES220</t>
+          <t>ES230</t>
         </is>
       </c>
       <c r="B96" t="n">
         <v>2</v>
       </c>
       <c r="C96" t="n">
-        <v>7440812.149004</v>
+        <v>2981362.408512</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ES220</t>
+          <t>ES230</t>
         </is>
       </c>
       <c r="B97" t="n">
         <v>3</v>
       </c>
       <c r="C97" t="n">
-        <v>10289782.118866</v>
+        <v>4122879.194722</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ES220</t>
+          <t>ES230</t>
         </is>
       </c>
       <c r="B98" t="n">
         <v>4</v>
       </c>
       <c r="C98" t="n">
-        <v>10008811.267613</v>
+        <v>4010300.632457</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ES220</t>
+          <t>ES230</t>
         </is>
       </c>
       <c r="B99" t="n">
         <v>5</v>
       </c>
       <c r="C99" t="n">
-        <v>10779080.852862</v>
+        <v>4318929.951394</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ES220</t>
+          <t>ES230</t>
         </is>
       </c>
       <c r="B100" t="n">
         <v>6</v>
       </c>
       <c r="C100" t="n">
-        <v>10589378.51087</v>
+        <v>4242920.583075</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ES220</t>
+          <t>ES230</t>
         </is>
       </c>
       <c r="B101" t="n">
         <v>7</v>
       </c>
       <c r="C101" t="n">
-        <v>12326030.783977</v>
+        <v>4938757.233701</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ES230</t>
+          <t>ES241</t>
         </is>
       </c>
       <c r="B102" t="n">
         <v>1</v>
       </c>
       <c r="C102" t="n">
-        <v>2724366.315664</v>
+        <v>1689289.967668</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ES230</t>
+          <t>ES241</t>
         </is>
       </c>
       <c r="B103" t="n">
         <v>2</v>
       </c>
       <c r="C103" t="n">
-        <v>2981362.408512</v>
+        <v>1848644.794103</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ES230</t>
+          <t>ES241</t>
         </is>
       </c>
       <c r="B104" t="n">
         <v>3</v>
       </c>
       <c r="C104" t="n">
-        <v>4122879.194722</v>
+        <v>2556461.817013</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ES230</t>
+          <t>ES241</t>
         </is>
       </c>
       <c r="B105" t="n">
         <v>4</v>
       </c>
       <c r="C105" t="n">
-        <v>4010300.632457</v>
+        <v>2486655.552447</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ES230</t>
+          <t>ES241</t>
         </is>
       </c>
       <c r="B106" t="n">
         <v>5</v>
       </c>
       <c r="C106" t="n">
-        <v>4318929.951394</v>
+        <v>2678026.444536</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ES230</t>
+          <t>ES241</t>
         </is>
       </c>
       <c r="B107" t="n">
         <v>6</v>
       </c>
       <c r="C107" t="n">
-        <v>4242920.583075</v>
+        <v>2630895.53464</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ES230</t>
+          <t>ES241</t>
         </is>
       </c>
       <c r="B108" t="n">
         <v>7</v>
       </c>
       <c r="C108" t="n">
-        <v>4938757.233701</v>
+        <v>3062360.960665</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ES241</t>
+          <t>ES242</t>
         </is>
       </c>
       <c r="B109" t="n">
         <v>1</v>
       </c>
       <c r="C109" t="n">
-        <v>1689289.967668</v>
+        <v>853527.876711</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ES241</t>
+          <t>ES242</t>
         </is>
       </c>
       <c r="B110" t="n">
         <v>2</v>
       </c>
       <c r="C110" t="n">
-        <v>1848644.794103</v>
+        <v>934043.234793</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ES241</t>
+          <t>ES242</t>
         </is>
       </c>
       <c r="B111" t="n">
         <v>3</v>
       </c>
       <c r="C111" t="n">
-        <v>2556461.817013</v>
+        <v>1291673.702165</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ES241</t>
+          <t>ES242</t>
         </is>
       </c>
       <c r="B112" t="n">
         <v>4</v>
       </c>
       <c r="C112" t="n">
-        <v>2486655.552447</v>
+        <v>1256403.503492</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ES241</t>
+          <t>ES242</t>
         </is>
       </c>
       <c r="B113" t="n">
         <v>5</v>
       </c>
       <c r="C113" t="n">
-        <v>2678026.444536</v>
+        <v>1353095.246364</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ES241</t>
+          <t>ES242</t>
         </is>
       </c>
       <c r="B114" t="n">
         <v>6</v>
       </c>
       <c r="C114" t="n">
-        <v>2630895.53464</v>
+        <v>1329281.960178</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ES241</t>
+          <t>ES242</t>
         </is>
       </c>
       <c r="B115" t="n">
         <v>7</v>
       </c>
       <c r="C115" t="n">
-        <v>3062360.960665</v>
+        <v>1547283.473238</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ES242</t>
+          <t>ES243</t>
         </is>
       </c>
       <c r="B116" t="n">
         <v>1</v>
       </c>
       <c r="C116" t="n">
-        <v>853527.876711</v>
+        <v>10046068.812295</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ES242</t>
+          <t>ES243</t>
         </is>
       </c>
       <c r="B117" t="n">
         <v>2</v>
       </c>
       <c r="C117" t="n">
-        <v>934043.234793</v>
+        <v>10993738.88823</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ES242</t>
+          <t>ES243</t>
         </is>
       </c>
       <c r="B118" t="n">
         <v>3</v>
       </c>
       <c r="C118" t="n">
-        <v>1291673.702165</v>
+        <v>15203068.63905</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ES242</t>
+          <t>ES243</t>
         </is>
       </c>
       <c r="B119" t="n">
         <v>4</v>
       </c>
       <c r="C119" t="n">
-        <v>1256403.503492</v>
+        <v>14787936.512069</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ES242</t>
+          <t>ES243</t>
         </is>
       </c>
       <c r="B120" t="n">
         <v>5</v>
       </c>
       <c r="C120" t="n">
-        <v>1353095.246364</v>
+        <v>15926003.503171</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ES242</t>
+          <t>ES243</t>
         </is>
       </c>
       <c r="B121" t="n">
         <v>6</v>
       </c>
       <c r="C121" t="n">
-        <v>1329281.960178</v>
+        <v>15645719.849642</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ES242</t>
+          <t>ES243</t>
         </is>
       </c>
       <c r="B122" t="n">
         <v>7</v>
       </c>
       <c r="C122" t="n">
-        <v>1547283.473238</v>
+        <v>18211609.331578</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ES243</t>
+          <t>ES300</t>
         </is>
       </c>
       <c r="B123" t="n">
         <v>1</v>
       </c>
       <c r="C123" t="n">
-        <v>10046068.812295</v>
+        <v>41322979.733795</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ES243</t>
+          <t>ES300</t>
         </is>
       </c>
       <c r="B124" t="n">
         <v>2</v>
       </c>
       <c r="C124" t="n">
-        <v>10993738.88823</v>
+        <v>45221076.797815</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ES243</t>
+          <t>ES300</t>
         </is>
       </c>
       <c r="B125" t="n">
         <v>3</v>
       </c>
       <c r="C125" t="n">
-        <v>15203068.63905</v>
+        <v>62535516.031312</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ES243</t>
+          <t>ES300</t>
         </is>
       </c>
       <c r="B126" t="n">
         <v>4</v>
       </c>
       <c r="C126" t="n">
-        <v>14787936.512069</v>
+        <v>60827933.016442</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ES243</t>
+          <t>ES300</t>
         </is>
       </c>
       <c r="B127" t="n">
         <v>5</v>
       </c>
       <c r="C127" t="n">
-        <v>15926003.503171</v>
+        <v>65509198.901407</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ES243</t>
+          <t>ES300</t>
         </is>
       </c>
       <c r="B128" t="n">
         <v>6</v>
       </c>
       <c r="C128" t="n">
-        <v>15645719.849642</v>
+        <v>64356294.621047</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ES243</t>
+          <t>ES300</t>
         </is>
       </c>
       <c r="B129" t="n">
         <v>7</v>
       </c>
       <c r="C129" t="n">
-        <v>18211609.331578</v>
+        <v>74910691.67349499</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ES300</t>
+          <t>ES412</t>
         </is>
       </c>
       <c r="B130" t="n">
         <v>1</v>
       </c>
       <c r="C130" t="n">
-        <v>41322979.733795</v>
+        <v>3447019.967636</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ES300</t>
+          <t>ES412</t>
         </is>
       </c>
       <c r="B131" t="n">
         <v>2</v>
       </c>
       <c r="C131" t="n">
-        <v>45221076.797815</v>
+        <v>3772185.735014</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ES300</t>
+          <t>ES412</t>
         </is>
       </c>
       <c r="B132" t="n">
         <v>3</v>
       </c>
       <c r="C132" t="n">
-        <v>62535516.031312</v>
+        <v>5216496.337753</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ES300</t>
+          <t>ES412</t>
         </is>
       </c>
       <c r="B133" t="n">
         <v>4</v>
       </c>
       <c r="C133" t="n">
-        <v>60827933.016442</v>
+        <v>5074055.671891</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ES300</t>
+          <t>ES412</t>
         </is>
       </c>
       <c r="B134" t="n">
         <v>5</v>
       </c>
       <c r="C134" t="n">
-        <v>65509198.901407</v>
+        <v>5464550.672088</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ES300</t>
+          <t>ES412</t>
         </is>
       </c>
       <c r="B135" t="n">
         <v>6</v>
       </c>
       <c r="C135" t="n">
-        <v>64356294.621047</v>
+        <v>5368379.386746</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ES300</t>
+          <t>ES412</t>
         </is>
       </c>
       <c r="B136" t="n">
         <v>7</v>
       </c>
       <c r="C136" t="n">
-        <v>74910691.67349499</v>
+        <v>6248790.664454</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ES412</t>
+          <t>ES413</t>
         </is>
       </c>
       <c r="B137" t="n">
         <v>1</v>
       </c>
       <c r="C137" t="n">
-        <v>3447019.967636</v>
+        <v>3409760.339981</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ES412</t>
+          <t>ES413</t>
         </is>
       </c>
       <c r="B138" t="n">
         <v>2</v>
       </c>
       <c r="C138" t="n">
-        <v>3772185.735014</v>
+        <v>3731411.316167</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ES412</t>
+          <t>ES413</t>
         </is>
       </c>
       <c r="B139" t="n">
         <v>3</v>
       </c>
       <c r="C139" t="n">
-        <v>5216496.337753</v>
+        <v>5160110.035081</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ES412</t>
+          <t>ES413</t>
         </is>
       </c>
       <c r="B140" t="n">
         <v>4</v>
       </c>
       <c r="C140" t="n">
-        <v>5074055.671891</v>
+        <v>5019209.042973</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ES412</t>
+          <t>ES413</t>
         </is>
       </c>
       <c r="B141" t="n">
         <v>5</v>
       </c>
       <c r="C141" t="n">
-        <v>5464550.672088</v>
+        <v>5405483.093351</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ES412</t>
+          <t>ES413</t>
         </is>
       </c>
       <c r="B142" t="n">
         <v>6</v>
       </c>
       <c r="C142" t="n">
-        <v>5368379.386746</v>
+        <v>5310351.34544</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ES412</t>
+          <t>ES413</t>
         </is>
       </c>
       <c r="B143" t="n">
         <v>7</v>
       </c>
       <c r="C143" t="n">
-        <v>6248790.664454</v>
+        <v>6181246.056172</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ES413</t>
+          <t>ES414</t>
         </is>
       </c>
       <c r="B144" t="n">
         <v>1</v>
       </c>
       <c r="C144" t="n">
-        <v>3409760.339981</v>
+        <v>1971426.004805</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ES413</t>
+          <t>ES414</t>
         </is>
       </c>
       <c r="B145" t="n">
         <v>2</v>
       </c>
       <c r="C145" t="n">
-        <v>3731411.316167</v>
+        <v>2157395.409015</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ES413</t>
+          <t>ES414</t>
         </is>
       </c>
       <c r="B146" t="n">
         <v>3</v>
       </c>
       <c r="C146" t="n">
-        <v>5160110.035081</v>
+        <v>2983428.187469</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ES413</t>
+          <t>ES414</t>
         </is>
       </c>
       <c r="B147" t="n">
         <v>4</v>
       </c>
       <c r="C147" t="n">
-        <v>5019209.042973</v>
+        <v>2901963.25966</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ES413</t>
+          <t>ES414</t>
         </is>
       </c>
       <c r="B148" t="n">
         <v>5</v>
       </c>
       <c r="C148" t="n">
-        <v>5405483.093351</v>
+        <v>3125295.878955</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ES413</t>
+          <t>ES414</t>
         </is>
       </c>
       <c r="B149" t="n">
         <v>6</v>
       </c>
       <c r="C149" t="n">
-        <v>5310351.34544</v>
+        <v>3070293.42042</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ES413</t>
+          <t>ES414</t>
         </is>
       </c>
       <c r="B150" t="n">
         <v>7</v>
       </c>
       <c r="C150" t="n">
-        <v>6181246.056172</v>
+        <v>3573819.858936</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ES414</t>
+          <t>ES415</t>
         </is>
       </c>
       <c r="B151" t="n">
         <v>1</v>
       </c>
       <c r="C151" t="n">
-        <v>1971426.004805</v>
+        <v>1796493.388664</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ES414</t>
+          <t>ES415</t>
         </is>
       </c>
       <c r="B152" t="n">
         <v>2</v>
       </c>
       <c r="C152" t="n">
-        <v>2157395.409015</v>
+        <v>1965960.97423</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ES414</t>
+          <t>ES415</t>
         </is>
       </c>
       <c r="B153" t="n">
         <v>3</v>
       </c>
       <c r="C153" t="n">
-        <v>2983428.187469</v>
+        <v>2718696.517789</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ES414</t>
+          <t>ES415</t>
         </is>
       </c>
       <c r="B154" t="n">
         <v>4</v>
       </c>
       <c r="C154" t="n">
-        <v>2901963.25966</v>
+        <v>2644460.303059</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ES414</t>
+          <t>ES415</t>
         </is>
       </c>
       <c r="B155" t="n">
         <v>5</v>
       </c>
       <c r="C155" t="n">
-        <v>3125295.878955</v>
+        <v>2847975.714268</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ES414</t>
+          <t>ES415</t>
         </is>
       </c>
       <c r="B156" t="n">
         <v>6</v>
       </c>
       <c r="C156" t="n">
-        <v>3070293.42042</v>
+        <v>2797853.846707</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ES414</t>
+          <t>ES415</t>
         </is>
       </c>
       <c r="B157" t="n">
         <v>7</v>
       </c>
       <c r="C157" t="n">
-        <v>3573819.858936</v>
+        <v>3256700.344424</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ES415</t>
+          <t>ES416</t>
         </is>
       </c>
       <c r="B158" t="n">
         <v>1</v>
       </c>
       <c r="C158" t="n">
-        <v>1796493.388664</v>
+        <v>2045981.955906</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ES415</t>
+          <t>ES416</t>
         </is>
       </c>
       <c r="B159" t="n">
         <v>2</v>
       </c>
       <c r="C159" t="n">
-        <v>1965960.97423</v>
+        <v>2238984.404101</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ES415</t>
+          <t>ES416</t>
         </is>
       </c>
       <c r="B160" t="n">
         <v>3</v>
       </c>
       <c r="C160" t="n">
-        <v>2718696.517789</v>
+        <v>3096256.32584</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ES415</t>
+          <t>ES416</t>
         </is>
       </c>
       <c r="B161" t="n">
         <v>4</v>
       </c>
       <c r="C161" t="n">
-        <v>2644460.303059</v>
+        <v>3011710.534149</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ES415</t>
+          <t>ES416</t>
         </is>
       </c>
       <c r="B162" t="n">
         <v>5</v>
       </c>
       <c r="C162" t="n">
-        <v>2847975.714268</v>
+        <v>3243489.210158</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ES415</t>
+          <t>ES416</t>
         </is>
       </c>
       <c r="B163" t="n">
         <v>6</v>
       </c>
       <c r="C163" t="n">
-        <v>2797853.846707</v>
+        <v>3186406.652954</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ES415</t>
+          <t>ES416</t>
         </is>
       </c>
       <c r="B164" t="n">
         <v>7</v>
       </c>
       <c r="C164" t="n">
-        <v>3256700.344424</v>
+        <v>3708975.597979</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ES416</t>
+          <t>ES417</t>
         </is>
       </c>
       <c r="B165" t="n">
         <v>1</v>
       </c>
       <c r="C165" t="n">
-        <v>2045981.955906</v>
+        <v>899357.043897</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ES416</t>
+          <t>ES417</t>
         </is>
       </c>
       <c r="B166" t="n">
         <v>2</v>
       </c>
       <c r="C166" t="n">
-        <v>2238984.404101</v>
+        <v>984195.5786520001</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ES416</t>
+          <t>ES417</t>
         </is>
       </c>
       <c r="B167" t="n">
         <v>3</v>
       </c>
       <c r="C167" t="n">
-        <v>3096256.32584</v>
+        <v>1361028.589874</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ES416</t>
+          <t>ES417</t>
         </is>
       </c>
       <c r="B168" t="n">
         <v>4</v>
       </c>
       <c r="C168" t="n">
-        <v>3011710.534149</v>
+        <v>1323864.599708</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ES416</t>
+          <t>ES417</t>
         </is>
       </c>
       <c r="B169" t="n">
         <v>5</v>
       </c>
       <c r="C169" t="n">
-        <v>3243489.210158</v>
+        <v>1425748.091052</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ES416</t>
+          <t>ES417</t>
         </is>
       </c>
       <c r="B170" t="n">
         <v>6</v>
       </c>
       <c r="C170" t="n">
-        <v>3186406.652954</v>
+        <v>1400656.178702</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ES416</t>
+          <t>ES417</t>
         </is>
       </c>
       <c r="B171" t="n">
         <v>7</v>
       </c>
       <c r="C171" t="n">
-        <v>3708975.597979</v>
+        <v>1630363.02449</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ES417</t>
+          <t>ES418</t>
         </is>
       </c>
       <c r="B172" t="n">
         <v>1</v>
       </c>
       <c r="C172" t="n">
-        <v>899357.043897</v>
+        <v>4412078.361863</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ES417</t>
+          <t>ES418</t>
         </is>
       </c>
       <c r="B173" t="n">
         <v>2</v>
       </c>
       <c r="C173" t="n">
-        <v>984195.5786520001</v>
+        <v>4828280.43198</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ES417</t>
+          <t>ES418</t>
         </is>
       </c>
       <c r="B174" t="n">
         <v>3</v>
       </c>
       <c r="C174" t="n">
-        <v>1361028.589874</v>
+        <v>6676953.087776</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ES417</t>
+          <t>ES418</t>
         </is>
       </c>
       <c r="B175" t="n">
         <v>4</v>
       </c>
       <c r="C175" t="n">
-        <v>1323864.599708</v>
+        <v>6494633.465147</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ES417</t>
+          <t>ES418</t>
         </is>
       </c>
       <c r="B176" t="n">
         <v>5</v>
       </c>
       <c r="C176" t="n">
-        <v>1425748.091052</v>
+        <v>6994454.92164</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ES417</t>
+          <t>ES418</t>
         </is>
       </c>
       <c r="B177" t="n">
         <v>6</v>
       </c>
       <c r="C177" t="n">
-        <v>1400656.178702</v>
+        <v>6871358.667172</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ES417</t>
+          <t>ES418</t>
         </is>
       </c>
       <c r="B178" t="n">
         <v>7</v>
       </c>
       <c r="C178" t="n">
-        <v>1630363.02449</v>
+        <v>7998257.723281</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ES418</t>
+          <t>ES419</t>
         </is>
       </c>
       <c r="B179" t="n">
         <v>1</v>
       </c>
       <c r="C179" t="n">
-        <v>4412078.361863</v>
+        <v>902054.158556</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ES418</t>
+          <t>ES419</t>
         </is>
       </c>
       <c r="B180" t="n">
         <v>2</v>
       </c>
       <c r="C180" t="n">
-        <v>4828280.43198</v>
+        <v>987147.118688</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ES418</t>
+          <t>ES419</t>
         </is>
       </c>
       <c r="B181" t="n">
         <v>3</v>
       </c>
       <c r="C181" t="n">
-        <v>6676953.087776</v>
+        <v>1365110.22818</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ES418</t>
+          <t>ES419</t>
         </is>
       </c>
       <c r="B182" t="n">
         <v>4</v>
       </c>
       <c r="C182" t="n">
-        <v>6494633.465147</v>
+        <v>1327834.785567</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ES418</t>
+          <t>ES419</t>
         </is>
       </c>
       <c r="B183" t="n">
         <v>5</v>
       </c>
       <c r="C183" t="n">
-        <v>6994454.92164</v>
+        <v>1430023.819031</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ES418</t>
+          <t>ES419</t>
         </is>
       </c>
       <c r="B184" t="n">
         <v>6</v>
       </c>
       <c r="C184" t="n">
-        <v>6871358.667172</v>
+        <v>1404856.65763</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ES418</t>
+          <t>ES419</t>
         </is>
       </c>
       <c r="B185" t="n">
         <v>7</v>
       </c>
       <c r="C185" t="n">
-        <v>7998257.723281</v>
+        <v>1635252.379661</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ES419</t>
+          <t>ES421</t>
         </is>
       </c>
       <c r="B186" t="n">
         <v>1</v>
       </c>
       <c r="C186" t="n">
-        <v>902054.158556</v>
+        <v>1618620.945019</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ES419</t>
+          <t>ES421</t>
         </is>
       </c>
       <c r="B187" t="n">
         <v>2</v>
       </c>
       <c r="C187" t="n">
-        <v>987147.118688</v>
+        <v>1771309.390871</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ES419</t>
+          <t>ES421</t>
         </is>
       </c>
       <c r="B188" t="n">
         <v>3</v>
       </c>
       <c r="C188" t="n">
-        <v>1365110.22818</v>
+        <v>2449515.903933</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ES419</t>
+          <t>ES421</t>
         </is>
       </c>
       <c r="B189" t="n">
         <v>4</v>
       </c>
       <c r="C189" t="n">
-        <v>1327834.785567</v>
+        <v>2382629.884314</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ES419</t>
+          <t>ES421</t>
         </is>
       </c>
       <c r="B190" t="n">
         <v>5</v>
       </c>
       <c r="C190" t="n">
-        <v>1430023.819031</v>
+        <v>2565995.049638</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ES419</t>
+          <t>ES421</t>
         </is>
       </c>
       <c r="B191" t="n">
         <v>6</v>
       </c>
       <c r="C191" t="n">
-        <v>1404856.65763</v>
+        <v>2520835.793752</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ES419</t>
+          <t>ES421</t>
         </is>
       </c>
       <c r="B192" t="n">
         <v>7</v>
       </c>
       <c r="C192" t="n">
-        <v>1635252.379661</v>
+        <v>2934251.482582</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ES421</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B193" t="n">
         <v>1</v>
       </c>
       <c r="C193" t="n">
-        <v>1618620.945019</v>
+        <v>4319149.56588</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ES421</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B194" t="n">
         <v>2</v>
       </c>
       <c r="C194" t="n">
-        <v>1771309.390871</v>
+        <v>4726585.436921</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>ES421</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B195" t="n">
         <v>3</v>
       </c>
       <c r="C195" t="n">
-        <v>2449515.903933</v>
+        <v>6536320.678197</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ES421</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B196" t="n">
         <v>4</v>
       </c>
       <c r="C196" t="n">
-        <v>2382629.884314</v>
+        <v>6357841.137639</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>ES421</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B197" t="n">
         <v>5</v>
       </c>
       <c r="C197" t="n">
-        <v>2565995.049638</v>
+        <v>6847135.173187</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ES421</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B198" t="n">
         <v>6</v>
       </c>
       <c r="C198" t="n">
-        <v>2520835.793752</v>
+        <v>6726631.616713</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ES421</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B199" t="n">
         <v>7</v>
       </c>
       <c r="C199" t="n">
-        <v>2934251.482582</v>
+        <v>7829795.515853</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES423</t>
         </is>
       </c>
       <c r="B200" t="n">
         <v>1</v>
       </c>
       <c r="C200" t="n">
-        <v>4319149.56588</v>
+        <v>1480949.750143</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES423</t>
         </is>
       </c>
       <c r="B201" t="n">
         <v>2</v>
       </c>
       <c r="C201" t="n">
-        <v>4726585.436921</v>
+        <v>1620651.337739</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES423</t>
         </is>
       </c>
       <c r="B202" t="n">
         <v>3</v>
       </c>
       <c r="C202" t="n">
-        <v>6536320.678197</v>
+        <v>2241173.251258</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES423</t>
         </is>
       </c>
       <c r="B203" t="n">
         <v>4</v>
       </c>
       <c r="C203" t="n">
-        <v>6357841.137639</v>
+        <v>2179976.196846</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES423</t>
         </is>
       </c>
       <c r="B204" t="n">
         <v>5</v>
       </c>
       <c r="C204" t="n">
-        <v>6847135.173187</v>
+        <v>2347745.307093</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES423</t>
         </is>
       </c>
       <c r="B205" t="n">
         <v>6</v>
       </c>
       <c r="C205" t="n">
-        <v>6726631.616713</v>
+        <v>2306427.054708</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES423</t>
         </is>
       </c>
       <c r="B206" t="n">
         <v>7</v>
       </c>
       <c r="C206" t="n">
-        <v>7829795.515853</v>
+        <v>2684679.827824</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ES423</t>
+          <t>ES424</t>
         </is>
       </c>
       <c r="B207" t="n">
         <v>1</v>
       </c>
       <c r="C207" t="n">
-        <v>1480949.750143</v>
+        <v>797218.4743530001</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ES423</t>
+          <t>ES424</t>
         </is>
       </c>
       <c r="B208" t="n">
         <v>2</v>
       </c>
       <c r="C208" t="n">
-        <v>1620651.337739</v>
+        <v>872422.029718</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ES423</t>
+          <t>ES424</t>
         </is>
       </c>
       <c r="B209" t="n">
         <v>3</v>
       </c>
       <c r="C209" t="n">
-        <v>2241173.251258</v>
+        <v>1206458.70662</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ES423</t>
+          <t>ES424</t>
         </is>
       </c>
       <c r="B210" t="n">
         <v>4</v>
       </c>
       <c r="C210" t="n">
-        <v>2179976.196846</v>
+        <v>1173515.372555</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ES423</t>
+          <t>ES424</t>
         </is>
       </c>
       <c r="B211" t="n">
         <v>5</v>
       </c>
       <c r="C211" t="n">
-        <v>2347745.307093</v>
+        <v>1263828.115511</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ES423</t>
+          <t>ES424</t>
         </is>
       </c>
       <c r="B212" t="n">
         <v>6</v>
       </c>
       <c r="C212" t="n">
-        <v>2306427.054708</v>
+        <v>1241585.85231</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ES423</t>
+          <t>ES424</t>
         </is>
       </c>
       <c r="B213" t="n">
         <v>7</v>
       </c>
       <c r="C213" t="n">
-        <v>2684679.827824</v>
+        <v>1445205.251736</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ES424</t>
+          <t>ES425</t>
         </is>
       </c>
       <c r="B214" t="n">
         <v>1</v>
       </c>
       <c r="C214" t="n">
-        <v>797218.4743530001</v>
+        <v>3759995.883676</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ES424</t>
+          <t>ES425</t>
         </is>
       </c>
       <c r="B215" t="n">
         <v>2</v>
       </c>
       <c r="C215" t="n">
-        <v>872422.029718</v>
+        <v>4114685.429524</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ES424</t>
+          <t>ES425</t>
         </is>
       </c>
       <c r="B216" t="n">
         <v>3</v>
       </c>
       <c r="C216" t="n">
-        <v>1206458.70662</v>
+        <v>5690133.779703</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ES424</t>
+          <t>ES425</t>
         </is>
       </c>
       <c r="B217" t="n">
         <v>4</v>
       </c>
       <c r="C217" t="n">
-        <v>1173515.372555</v>
+        <v>5534760.059117</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>ES424</t>
+          <t>ES425</t>
         </is>
       </c>
       <c r="B218" t="n">
         <v>5</v>
       </c>
       <c r="C218" t="n">
-        <v>1263828.115511</v>
+        <v>5960710.476325</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ES424</t>
+          <t>ES425</t>
         </is>
       </c>
       <c r="B219" t="n">
         <v>6</v>
       </c>
       <c r="C219" t="n">
-        <v>1241585.85231</v>
+        <v>5855807.214838</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ES424</t>
+          <t>ES425</t>
         </is>
       </c>
       <c r="B220" t="n">
         <v>7</v>
       </c>
       <c r="C220" t="n">
-        <v>1445205.251736</v>
+        <v>6816156.389257</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ES425</t>
+          <t>ES431</t>
         </is>
       </c>
       <c r="B221" t="n">
         <v>1</v>
       </c>
       <c r="C221" t="n">
-        <v>3759995.883676</v>
+        <v>3230941.772713</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>ES425</t>
+          <t>ES431</t>
         </is>
       </c>
       <c r="B222" t="n">
         <v>2</v>
       </c>
       <c r="C222" t="n">
-        <v>4114685.429524</v>
+        <v>3535724.359045</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ES425</t>
+          <t>ES431</t>
         </is>
       </c>
       <c r="B223" t="n">
         <v>3</v>
       </c>
       <c r="C223" t="n">
-        <v>5690133.779703</v>
+        <v>4889497.619129</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>ES425</t>
+          <t>ES431</t>
         </is>
       </c>
       <c r="B224" t="n">
         <v>4</v>
       </c>
       <c r="C224" t="n">
-        <v>5534760.059117</v>
+        <v>4755985.91865</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>ES425</t>
+          <t>ES431</t>
         </is>
       </c>
       <c r="B225" t="n">
         <v>5</v>
       </c>
       <c r="C225" t="n">
-        <v>5960710.476325</v>
+        <v>5122002.54171</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>ES425</t>
+          <t>ES431</t>
         </is>
       </c>
       <c r="B226" t="n">
         <v>6</v>
       </c>
       <c r="C226" t="n">
-        <v>5855807.214838</v>
+        <v>5031859.802165</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>ES425</t>
+          <t>ES431</t>
         </is>
       </c>
       <c r="B227" t="n">
         <v>7</v>
       </c>
       <c r="C227" t="n">
-        <v>6816156.389257</v>
+        <v>5857082.052405</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>ES431</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="B228" t="n">
         <v>1</v>
       </c>
       <c r="C228" t="n">
-        <v>3230941.772713</v>
+        <v>1555344.048263</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>ES431</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="B229" t="n">
         <v>2</v>
       </c>
       <c r="C229" t="n">
-        <v>3535724.359045</v>
+        <v>1702063.430726</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>ES431</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="B230" t="n">
         <v>3</v>
       </c>
       <c r="C230" t="n">
-        <v>4889497.619129</v>
+        <v>2353756.754496</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>ES431</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="B231" t="n">
         <v>4</v>
       </c>
       <c r="C231" t="n">
-        <v>4755985.91865</v>
+        <v>2289485.516163</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>ES431</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="B232" t="n">
         <v>5</v>
       </c>
       <c r="C232" t="n">
-        <v>5122002.54171</v>
+        <v>2465682.370297</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>ES431</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="B233" t="n">
         <v>6</v>
       </c>
       <c r="C233" t="n">
-        <v>5031859.802165</v>
+        <v>2422288.529334</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>ES431</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="B234" t="n">
         <v>7</v>
       </c>
       <c r="C234" t="n">
-        <v>5857082.052405</v>
+        <v>2819542.5208</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>ES511</t>
         </is>
       </c>
       <c r="B235" t="n">
         <v>1</v>
       </c>
       <c r="C235" t="n">
-        <v>1555344.048263</v>
+        <v>39092284.695687</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>ES511</t>
         </is>
       </c>
       <c r="B236" t="n">
         <v>2</v>
       </c>
       <c r="C236" t="n">
-        <v>1702063.430726</v>
+        <v>42779954.877745</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>ES511</t>
         </is>
       </c>
       <c r="B237" t="n">
         <v>3</v>
       </c>
       <c r="C237" t="n">
-        <v>2353756.754496</v>
+        <v>59159726.913121</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>ES511</t>
         </is>
       </c>
       <c r="B238" t="n">
         <v>4</v>
       </c>
       <c r="C238" t="n">
-        <v>2289485.516163</v>
+        <v>57544322.559687</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>ES511</t>
         </is>
       </c>
       <c r="B239" t="n">
         <v>5</v>
       </c>
       <c r="C239" t="n">
-        <v>2465682.370297</v>
+        <v>61972884.582324</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>ES511</t>
         </is>
       </c>
       <c r="B240" t="n">
         <v>6</v>
       </c>
       <c r="C240" t="n">
-        <v>2422288.529334</v>
+        <v>60882216.323523</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>ES511</t>
         </is>
       </c>
       <c r="B241" t="n">
         <v>7</v>
       </c>
       <c r="C241" t="n">
-        <v>2819542.5208</v>
+        <v>70866866.43887299</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>ES511</t>
+          <t>ES512</t>
         </is>
       </c>
       <c r="B242" t="n">
         <v>1</v>
       </c>
       <c r="C242" t="n">
-        <v>39092284.695687</v>
+        <v>4501303.270715</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>ES511</t>
+          <t>ES512</t>
         </is>
       </c>
       <c r="B243" t="n">
         <v>2</v>
       </c>
       <c r="C243" t="n">
-        <v>42779954.877745</v>
+        <v>4925922.143238</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>ES511</t>
+          <t>ES512</t>
         </is>
       </c>
       <c r="B244" t="n">
         <v>3</v>
       </c>
       <c r="C244" t="n">
-        <v>59159726.913121</v>
+        <v>6811980.274921</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>ES511</t>
+          <t>ES512</t>
         </is>
       </c>
       <c r="B245" t="n">
         <v>4</v>
       </c>
       <c r="C245" t="n">
-        <v>57544322.559687</v>
+        <v>6625973.625368</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>ES511</t>
+          <t>ES512</t>
         </is>
       </c>
       <c r="B246" t="n">
         <v>5</v>
       </c>
       <c r="C246" t="n">
-        <v>61972884.582324</v>
+        <v>7135902.908658</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>ES511</t>
+          <t>ES512</t>
         </is>
       </c>
       <c r="B247" t="n">
         <v>6</v>
       </c>
       <c r="C247" t="n">
-        <v>60882216.323523</v>
+        <v>7010317.294033</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>ES511</t>
+          <t>ES512</t>
         </is>
       </c>
       <c r="B248" t="n">
         <v>7</v>
       </c>
       <c r="C248" t="n">
-        <v>70866866.43887299</v>
+        <v>8160005.488802</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>ES512</t>
+          <t>ES513</t>
         </is>
       </c>
       <c r="B249" t="n">
         <v>1</v>
       </c>
       <c r="C249" t="n">
-        <v>4501303.270715</v>
+        <v>4049245.648555</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>ES512</t>
+          <t>ES513</t>
         </is>
       </c>
       <c r="B250" t="n">
         <v>2</v>
       </c>
       <c r="C250" t="n">
-        <v>4925922.143238</v>
+        <v>4431220.827398</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>ES512</t>
+          <t>ES513</t>
         </is>
       </c>
       <c r="B251" t="n">
         <v>3</v>
       </c>
       <c r="C251" t="n">
-        <v>6811980.274921</v>
+        <v>6127865.604107</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>ES512</t>
+          <t>ES513</t>
         </is>
       </c>
       <c r="B252" t="n">
         <v>4</v>
       </c>
       <c r="C252" t="n">
-        <v>6625973.625368</v>
+        <v>5960539.260821</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>ES512</t>
+          <t>ES513</t>
         </is>
       </c>
       <c r="B253" t="n">
         <v>5</v>
       </c>
       <c r="C253" t="n">
-        <v>7135902.908658</v>
+        <v>6419257.282526</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>ES512</t>
+          <t>ES513</t>
         </is>
       </c>
       <c r="B254" t="n">
         <v>6</v>
       </c>
       <c r="C254" t="n">
-        <v>7010317.294033</v>
+        <v>6306284.000577</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>ES512</t>
+          <t>ES513</t>
         </is>
       </c>
       <c r="B255" t="n">
         <v>7</v>
       </c>
       <c r="C255" t="n">
-        <v>8160005.488802</v>
+        <v>7340511.121009</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>ES513</t>
+          <t>ES514</t>
         </is>
       </c>
       <c r="B256" t="n">
         <v>1</v>
       </c>
       <c r="C256" t="n">
-        <v>4049245.648555</v>
+        <v>7925937.807573</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>ES513</t>
+          <t>ES514</t>
         </is>
       </c>
       <c r="B257" t="n">
         <v>2</v>
       </c>
       <c r="C257" t="n">
-        <v>4431220.827398</v>
+        <v>8673610.775407</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>ES513</t>
+          <t>ES514</t>
         </is>
       </c>
       <c r="B258" t="n">
         <v>3</v>
       </c>
       <c r="C258" t="n">
-        <v>6127865.604107</v>
+        <v>11994599.954351</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>ES513</t>
+          <t>ES514</t>
         </is>
       </c>
       <c r="B259" t="n">
         <v>4</v>
       </c>
       <c r="C259" t="n">
-        <v>5960539.260821</v>
+        <v>11667077.668584</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>ES513</t>
+          <t>ES514</t>
         </is>
       </c>
       <c r="B260" t="n">
         <v>5</v>
       </c>
       <c r="C260" t="n">
-        <v>6419257.282526</v>
+        <v>12564966.022811</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>ES513</t>
+          <t>ES514</t>
         </is>
       </c>
       <c r="B261" t="n">
         <v>6</v>
       </c>
       <c r="C261" t="n">
-        <v>6306284.000577</v>
+        <v>12343833.67265</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>ES513</t>
+          <t>ES514</t>
         </is>
       </c>
       <c r="B262" t="n">
         <v>7</v>
       </c>
       <c r="C262" t="n">
-        <v>7340511.121009</v>
+        <v>14368215.630897</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>ES514</t>
+          <t>ES521</t>
         </is>
       </c>
       <c r="B263" t="n">
         <v>1</v>
       </c>
       <c r="C263" t="n">
-        <v>7925937.807573</v>
+        <v>6354065.861456</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ES514</t>
+          <t>ES521</t>
         </is>
       </c>
       <c r="B264" t="n">
         <v>2</v>
       </c>
       <c r="C264" t="n">
-        <v>8673610.775407</v>
+        <v>6953460.330071</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>ES514</t>
+          <t>ES521</t>
         </is>
       </c>
       <c r="B265" t="n">
         <v>3</v>
       </c>
       <c r="C265" t="n">
-        <v>11994599.954351</v>
+        <v>9615830.951757999</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>ES514</t>
+          <t>ES521</t>
         </is>
       </c>
       <c r="B266" t="n">
         <v>4</v>
       </c>
       <c r="C266" t="n">
-        <v>11667077.668584</v>
+        <v>9353262.884056</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>ES514</t>
+          <t>ES521</t>
         </is>
       </c>
       <c r="B267" t="n">
         <v>5</v>
       </c>
       <c r="C267" t="n">
-        <v>12564966.022811</v>
+        <v>10073082.024391</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>ES514</t>
+          <t>ES521</t>
         </is>
       </c>
       <c r="B268" t="n">
         <v>6</v>
       </c>
       <c r="C268" t="n">
-        <v>12343833.67265</v>
+        <v>9895804.640800999</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>ES514</t>
+          <t>ES521</t>
         </is>
       </c>
       <c r="B269" t="n">
         <v>7</v>
       </c>
       <c r="C269" t="n">
-        <v>14368215.630897</v>
+        <v>11518711.179275</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>ES521</t>
+          <t>ES522</t>
         </is>
       </c>
       <c r="B270" t="n">
         <v>1</v>
       </c>
       <c r="C270" t="n">
-        <v>6354065.861456</v>
+        <v>5624922.363235</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>ES521</t>
+          <t>ES522</t>
         </is>
       </c>
       <c r="B271" t="n">
         <v>2</v>
       </c>
       <c r="C271" t="n">
-        <v>6953460.330071</v>
+        <v>6155534.954357</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>ES521</t>
+          <t>ES522</t>
         </is>
       </c>
       <c r="B272" t="n">
         <v>3</v>
       </c>
       <c r="C272" t="n">
-        <v>9615830.951757999</v>
+        <v>8512392.496548001</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>ES521</t>
+          <t>ES522</t>
         </is>
       </c>
       <c r="B273" t="n">
         <v>4</v>
       </c>
       <c r="C273" t="n">
-        <v>9353262.884056</v>
+        <v>8279954.711342</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>ES521</t>
+          <t>ES522</t>
         </is>
       </c>
       <c r="B274" t="n">
         <v>5</v>
       </c>
       <c r="C274" t="n">
-        <v>10073082.024391</v>
+        <v>8917172.969420999</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>ES521</t>
+          <t>ES522</t>
         </is>
       </c>
       <c r="B275" t="n">
         <v>6</v>
       </c>
       <c r="C275" t="n">
-        <v>9895804.640800999</v>
+        <v>8760238.568488</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>ES521</t>
+          <t>ES522</t>
         </is>
       </c>
       <c r="B276" t="n">
         <v>7</v>
       </c>
       <c r="C276" t="n">
-        <v>11518711.179275</v>
+        <v>10196912.893361</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>ES522</t>
+          <t>ES523</t>
         </is>
       </c>
       <c r="B277" t="n">
         <v>1</v>
       </c>
       <c r="C277" t="n">
-        <v>5624922.363235</v>
+        <v>12683690.826904</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>ES522</t>
+          <t>ES523</t>
         </is>
       </c>
       <c r="B278" t="n">
         <v>2</v>
       </c>
       <c r="C278" t="n">
-        <v>6155534.954357</v>
+        <v>13880174.19504</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>ES522</t>
+          <t>ES523</t>
         </is>
       </c>
       <c r="B279" t="n">
         <v>3</v>
       </c>
       <c r="C279" t="n">
-        <v>8512392.496548001</v>
+        <v>19194674.637497</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>ES522</t>
+          <t>ES523</t>
         </is>
       </c>
       <c r="B280" t="n">
         <v>4</v>
       </c>
       <c r="C280" t="n">
-        <v>8279954.711342</v>
+        <v>18670548.469408</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>ES522</t>
+          <t>ES523</t>
         </is>
       </c>
       <c r="B281" t="n">
         <v>5</v>
       </c>
       <c r="C281" t="n">
-        <v>8917172.969420999</v>
+        <v>20107417.967831</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>ES522</t>
+          <t>ES523</t>
         </is>
       </c>
       <c r="B282" t="n">
         <v>6</v>
       </c>
       <c r="C282" t="n">
-        <v>8760238.568488</v>
+        <v>19753545.097595</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>ES522</t>
+          <t>ES523</t>
         </is>
       </c>
       <c r="B283" t="n">
         <v>7</v>
       </c>
       <c r="C283" t="n">
-        <v>10196912.893361</v>
+        <v>22993115.669225</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>ES523</t>
+          <t>ES532</t>
         </is>
       </c>
       <c r="B284" t="n">
         <v>1</v>
       </c>
       <c r="C284" t="n">
-        <v>12683690.826904</v>
+        <v>4323983.291979</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>ES523</t>
+          <t>ES532</t>
         </is>
       </c>
       <c r="B285" t="n">
         <v>2</v>
       </c>
       <c r="C285" t="n">
-        <v>13880174.19504</v>
+        <v>4731875.140145</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>ES523</t>
+          <t>ES532</t>
         </is>
       </c>
       <c r="B286" t="n">
         <v>3</v>
       </c>
       <c r="C286" t="n">
-        <v>19194674.637497</v>
+        <v>6543635.725609</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>ES523</t>
+          <t>ES532</t>
         </is>
       </c>
       <c r="B287" t="n">
         <v>4</v>
       </c>
       <c r="C287" t="n">
-        <v>18670548.469408</v>
+        <v>6364956.441745</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>ES523</t>
+          <t>ES532</t>
         </is>
       </c>
       <c r="B288" t="n">
         <v>5</v>
       </c>
       <c r="C288" t="n">
-        <v>20107417.967831</v>
+        <v>6854798.065033</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>ES523</t>
+          <t>ES532</t>
         </is>
       </c>
       <c r="B289" t="n">
         <v>6</v>
       </c>
       <c r="C289" t="n">
-        <v>19753545.097595</v>
+        <v>6734159.648403</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>ES523</t>
+          <t>ES532</t>
         </is>
       </c>
       <c r="B290" t="n">
         <v>7</v>
       </c>
       <c r="C290" t="n">
-        <v>22993115.669225</v>
+        <v>7838558.140614</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>ES532</t>
+          <t>ES611</t>
         </is>
       </c>
       <c r="B291" t="n">
         <v>1</v>
       </c>
       <c r="C291" t="n">
-        <v>4323983.291979</v>
+        <v>3772724.46836</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>ES532</t>
+          <t>ES611</t>
         </is>
       </c>
       <c r="B292" t="n">
         <v>2</v>
       </c>
       <c r="C292" t="n">
-        <v>4731875.140145</v>
+        <v>4128614.732524</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>ES532</t>
+          <t>ES611</t>
         </is>
       </c>
       <c r="B293" t="n">
         <v>3</v>
       </c>
       <c r="C293" t="n">
-        <v>6543635.725609</v>
+        <v>5709396.393792</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>ES532</t>
+          <t>ES611</t>
         </is>
       </c>
       <c r="B294" t="n">
         <v>4</v>
       </c>
       <c r="C294" t="n">
-        <v>6364956.441745</v>
+        <v>5553496.691896</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>ES532</t>
+          <t>ES611</t>
         </is>
       </c>
       <c r="B295" t="n">
         <v>5</v>
       </c>
       <c r="C295" t="n">
-        <v>6854798.065033</v>
+        <v>5980889.064394</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>ES532</t>
+          <t>ES611</t>
         </is>
       </c>
       <c r="B296" t="n">
         <v>6</v>
       </c>
       <c r="C296" t="n">
-        <v>6734159.648403</v>
+        <v>5875630.677506</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>ES532</t>
+          <t>ES611</t>
         </is>
       </c>
       <c r="B297" t="n">
         <v>7</v>
       </c>
       <c r="C297" t="n">
-        <v>7838558.140614</v>
+        <v>6839230.888939</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>ES611</t>
+          <t>ES612</t>
         </is>
       </c>
       <c r="B298" t="n">
         <v>1</v>
       </c>
       <c r="C298" t="n">
-        <v>3772724.46836</v>
+        <v>4402392.804954</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>ES611</t>
+          <t>ES612</t>
         </is>
       </c>
       <c r="B299" t="n">
         <v>2</v>
       </c>
       <c r="C299" t="n">
-        <v>4128614.732524</v>
+        <v>4817681.212958</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>ES611</t>
+          <t>ES612</t>
         </is>
       </c>
       <c r="B300" t="n">
         <v>3</v>
       </c>
       <c r="C300" t="n">
-        <v>5709396.393792</v>
+        <v>6662295.594457</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>ES611</t>
+          <t>ES612</t>
         </is>
       </c>
       <c r="B301" t="n">
         <v>4</v>
       </c>
       <c r="C301" t="n">
-        <v>5553496.691896</v>
+        <v>6480376.206578</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>ES611</t>
+          <t>ES612</t>
         </is>
       </c>
       <c r="B302" t="n">
         <v>5</v>
       </c>
       <c r="C302" t="n">
-        <v>5980889.064394</v>
+        <v>6979100.436602</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>ES611</t>
+          <t>ES612</t>
         </is>
       </c>
       <c r="B303" t="n">
         <v>6</v>
       </c>
       <c r="C303" t="n">
-        <v>5875630.677506</v>
+        <v>6856274.407566</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>ES611</t>
+          <t>ES612</t>
         </is>
       </c>
       <c r="B304" t="n">
         <v>7</v>
       </c>
       <c r="C304" t="n">
-        <v>6839230.888939</v>
+        <v>7980699.653365</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>ES612</t>
+          <t>ES613</t>
         </is>
       </c>
       <c r="B305" t="n">
         <v>1</v>
       </c>
       <c r="C305" t="n">
-        <v>4402392.804954</v>
+        <v>2496128.168362</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>ES612</t>
+          <t>ES613</t>
         </is>
       </c>
       <c r="B306" t="n">
         <v>2</v>
       </c>
       <c r="C306" t="n">
-        <v>4817681.212958</v>
+        <v>2731594.002317</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>ES612</t>
+          <t>ES613</t>
         </is>
       </c>
       <c r="B307" t="n">
         <v>3</v>
       </c>
       <c r="C307" t="n">
-        <v>6662295.594457</v>
+        <v>3777478.393243</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>ES612</t>
+          <t>ES613</t>
         </is>
       </c>
       <c r="B308" t="n">
         <v>4</v>
       </c>
       <c r="C308" t="n">
-        <v>6480376.206578</v>
+        <v>3674331.280167</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>ES612</t>
+          <t>ES613</t>
         </is>
       </c>
       <c r="B309" t="n">
         <v>5</v>
       </c>
       <c r="C309" t="n">
-        <v>6979100.436602</v>
+        <v>3957104.684078</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>ES612</t>
+          <t>ES613</t>
         </is>
       </c>
       <c r="B310" t="n">
         <v>6</v>
       </c>
       <c r="C310" t="n">
-        <v>6856274.407566</v>
+        <v>3887463.122211</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>ES612</t>
+          <t>ES613</t>
         </is>
       </c>
       <c r="B311" t="n">
         <v>7</v>
       </c>
       <c r="C311" t="n">
-        <v>7980699.653365</v>
+        <v>4525004.944036</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>ES613</t>
+          <t>ES614</t>
         </is>
       </c>
       <c r="B312" t="n">
         <v>1</v>
       </c>
       <c r="C312" t="n">
-        <v>2496128.168362</v>
+        <v>4242425.023711</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>ES613</t>
+          <t>ES614</t>
         </is>
       </c>
       <c r="B313" t="n">
         <v>2</v>
       </c>
       <c r="C313" t="n">
-        <v>2731594.002317</v>
+        <v>4642623.282302</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>ES613</t>
+          <t>ES614</t>
         </is>
       </c>
       <c r="B314" t="n">
         <v>3</v>
       </c>
       <c r="C314" t="n">
-        <v>3777478.393243</v>
+        <v>6420210.734827</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>ES613</t>
+          <t>ES614</t>
         </is>
       </c>
       <c r="B315" t="n">
         <v>4</v>
       </c>
       <c r="C315" t="n">
-        <v>3674331.280167</v>
+        <v>6244901.670499</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>ES613</t>
+          <t>ES614</t>
         </is>
       </c>
       <c r="B316" t="n">
         <v>5</v>
       </c>
       <c r="C316" t="n">
-        <v>3957104.684078</v>
+        <v>6725503.980908</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>ES613</t>
+          <t>ES614</t>
         </is>
       </c>
       <c r="B317" t="n">
         <v>6</v>
       </c>
       <c r="C317" t="n">
-        <v>3887463.122211</v>
+        <v>6607141.026434</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>ES613</t>
+          <t>ES614</t>
         </is>
       </c>
       <c r="B318" t="n">
         <v>7</v>
       </c>
       <c r="C318" t="n">
-        <v>4525004.944036</v>
+        <v>7690708.534246</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>ES614</t>
+          <t>ES615</t>
         </is>
       </c>
       <c r="B319" t="n">
         <v>1</v>
       </c>
       <c r="C319" t="n">
-        <v>4242425.023711</v>
+        <v>3277873.034142</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>ES614</t>
+          <t>ES615</t>
         </is>
       </c>
       <c r="B320" t="n">
         <v>2</v>
       </c>
       <c r="C320" t="n">
-        <v>4642623.282302</v>
+        <v>3587082.760376</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>ES614</t>
+          <t>ES615</t>
         </is>
       </c>
       <c r="B321" t="n">
         <v>3</v>
       </c>
       <c r="C321" t="n">
-        <v>6420210.734827</v>
+        <v>4960520.344751</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>ES614</t>
+          <t>ES615</t>
         </is>
       </c>
       <c r="B322" t="n">
         <v>4</v>
       </c>
       <c r="C322" t="n">
-        <v>6244901.670499</v>
+        <v>4825069.311112</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>ES614</t>
+          <t>ES615</t>
         </is>
       </c>
       <c r="B323" t="n">
         <v>5</v>
       </c>
       <c r="C323" t="n">
-        <v>6725503.980908</v>
+        <v>5196402.533179</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>ES614</t>
+          <t>ES615</t>
         </is>
       </c>
       <c r="B324" t="n">
         <v>6</v>
       </c>
       <c r="C324" t="n">
-        <v>6607141.026434</v>
+        <v>5104950.419225</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>ES614</t>
+          <t>ES615</t>
         </is>
       </c>
       <c r="B325" t="n">
         <v>7</v>
       </c>
       <c r="C325" t="n">
-        <v>7690708.534246</v>
+        <v>5942159.490611</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>ES615</t>
+          <t>ES616</t>
         </is>
       </c>
       <c r="B326" t="n">
         <v>1</v>
       </c>
       <c r="C326" t="n">
-        <v>3277873.034142</v>
+        <v>2564489.690012</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>ES615</t>
+          <t>ES616</t>
         </is>
       </c>
       <c r="B327" t="n">
         <v>2</v>
       </c>
       <c r="C327" t="n">
-        <v>3587082.760376</v>
+        <v>2806404.232374</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>ES615</t>
+          <t>ES616</t>
         </is>
       </c>
       <c r="B328" t="n">
         <v>3</v>
       </c>
       <c r="C328" t="n">
-        <v>4960520.344751</v>
+        <v>3880932.284046</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>ES615</t>
+          <t>ES616</t>
         </is>
       </c>
       <c r="B329" t="n">
         <v>4</v>
       </c>
       <c r="C329" t="n">
-        <v>4825069.311112</v>
+        <v>3774960.278526</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>ES615</t>
+          <t>ES616</t>
         </is>
       </c>
       <c r="B330" t="n">
         <v>5</v>
       </c>
       <c r="C330" t="n">
-        <v>5196402.533179</v>
+        <v>4065478.00439</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>ES615</t>
+          <t>ES616</t>
         </is>
       </c>
       <c r="B331" t="n">
         <v>6</v>
       </c>
       <c r="C331" t="n">
-        <v>5104950.419225</v>
+        <v>3993929.167409</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>ES615</t>
+          <t>ES616</t>
         </is>
       </c>
       <c r="B332" t="n">
         <v>7</v>
       </c>
       <c r="C332" t="n">
-        <v>5942159.490611</v>
+        <v>4648931.362305</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>ES616</t>
+          <t>ES617</t>
         </is>
       </c>
       <c r="B333" t="n">
         <v>1</v>
       </c>
       <c r="C333" t="n">
-        <v>2564489.690012</v>
+        <v>5324415.328105</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>ES616</t>
+          <t>ES617</t>
         </is>
       </c>
       <c r="B334" t="n">
         <v>2</v>
       </c>
       <c r="C334" t="n">
-        <v>2806404.232374</v>
+        <v>5826680.360583</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>ES616</t>
+          <t>ES617</t>
         </is>
       </c>
       <c r="B335" t="n">
         <v>3</v>
       </c>
       <c r="C335" t="n">
-        <v>3880932.284046</v>
+        <v>8057624.649844</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>ES616</t>
+          <t>ES617</t>
         </is>
       </c>
       <c r="B336" t="n">
         <v>4</v>
       </c>
       <c r="C336" t="n">
-        <v>3774960.278526</v>
+        <v>7837604.669752</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>ES616</t>
+          <t>ES617</t>
         </is>
       </c>
       <c r="B337" t="n">
         <v>5</v>
       </c>
       <c r="C337" t="n">
-        <v>4065478.00439</v>
+        <v>8440780.045618</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>ES616</t>
+          <t>ES617</t>
         </is>
       </c>
       <c r="B338" t="n">
         <v>6</v>
       </c>
       <c r="C338" t="n">
-        <v>3993929.167409</v>
+        <v>8292229.741121</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>ES616</t>
+          <t>ES617</t>
         </is>
       </c>
       <c r="B339" t="n">
         <v>7</v>
       </c>
       <c r="C339" t="n">
-        <v>4648931.362305</v>
+        <v>9652150.874761</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>ES617</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B340" t="n">
         <v>1</v>
       </c>
       <c r="C340" t="n">
-        <v>5324415.328105</v>
+        <v>7637307.603326</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>ES617</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B341" t="n">
         <v>2</v>
       </c>
       <c r="C341" t="n">
-        <v>5826680.360583</v>
+        <v>8357753.382826</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>ES617</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B342" t="n">
         <v>3</v>
       </c>
       <c r="C342" t="n">
-        <v>8057624.649844</v>
+        <v>11557805.732806</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>ES617</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B343" t="n">
         <v>4</v>
       </c>
       <c r="C343" t="n">
-        <v>7837604.669752</v>
+        <v>11242210.467731</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>ES617</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B344" t="n">
         <v>5</v>
       </c>
       <c r="C344" t="n">
-        <v>8440780.045618</v>
+        <v>12107401.404269</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>ES617</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B345" t="n">
         <v>6</v>
       </c>
       <c r="C345" t="n">
-        <v>8292229.741121</v>
+        <v>11894321.788931</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>ES617</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B346" t="n">
         <v>7</v>
       </c>
       <c r="C346" t="n">
-        <v>9652150.874761</v>
+        <v>13844984.044569</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>ES618</t>
+          <t>ES620</t>
         </is>
       </c>
       <c r="B347" t="n">
         <v>1</v>
       </c>
       <c r="C347" t="n">
-        <v>7637307.603326</v>
+        <v>6195161.162227</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>ES618</t>
+          <t>ES620</t>
         </is>
       </c>
       <c r="B348" t="n">
         <v>2</v>
       </c>
       <c r="C348" t="n">
-        <v>8357753.382826</v>
+        <v>6779565.764537</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>ES618</t>
+          <t>ES620</t>
         </is>
       </c>
       <c r="B349" t="n">
         <v>3</v>
       </c>
       <c r="C349" t="n">
-        <v>11557805.732806</v>
+        <v>9375354.891462</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>ES618</t>
+          <t>ES620</t>
         </is>
       </c>
       <c r="B350" t="n">
         <v>4</v>
       </c>
       <c r="C350" t="n">
-        <v>11242210.467731</v>
+        <v>9119353.217739999</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>ES618</t>
+          <t>ES620</t>
         </is>
       </c>
       <c r="B351" t="n">
         <v>5</v>
       </c>
       <c r="C351" t="n">
-        <v>12107401.404269</v>
+        <v>9821170.869503001</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>ES618</t>
+          <t>ES620</t>
         </is>
       </c>
       <c r="B352" t="n">
         <v>6</v>
       </c>
       <c r="C352" t="n">
-        <v>11894321.788931</v>
+        <v>9648326.900663</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>ES618</t>
+          <t>ES620</t>
         </is>
       </c>
       <c r="B353" t="n">
         <v>7</v>
       </c>
       <c r="C353" t="n">
-        <v>13844984.044569</v>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>ES620</t>
-        </is>
-      </c>
-      <c r="B354" t="n">
-        <v>1</v>
-      </c>
-      <c r="C354" t="n">
-        <v>6195161.162227</v>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>ES620</t>
-        </is>
-      </c>
-      <c r="B355" t="n">
-        <v>2</v>
-      </c>
-      <c r="C355" t="n">
-        <v>6779565.764537</v>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>ES620</t>
-        </is>
-      </c>
-      <c r="B356" t="n">
-        <v>3</v>
-      </c>
-      <c r="C356" t="n">
-        <v>9375354.891462</v>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>ES620</t>
-        </is>
-      </c>
-      <c r="B357" t="n">
-        <v>4</v>
-      </c>
-      <c r="C357" t="n">
-        <v>9119353.217739999</v>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>ES620</t>
-        </is>
-      </c>
-      <c r="B358" t="n">
-        <v>5</v>
-      </c>
-      <c r="C358" t="n">
-        <v>9821170.869503001</v>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>ES620</t>
-        </is>
-      </c>
-      <c r="B359" t="n">
-        <v>6</v>
-      </c>
-      <c r="C359" t="n">
-        <v>9648326.900663</v>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>ES620</t>
-        </is>
-      </c>
-      <c r="B360" t="n">
-        <v>7</v>
-      </c>
-      <c r="C360" t="n">
         <v>11230647.225366</v>
       </c>
     </row>
@@ -5105,7 +5014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5159,7 +5068,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -5172,7 +5081,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -5185,7 +5094,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5198,7 +5107,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES112</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5211,7 +5120,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ES112</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5224,7 +5133,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES114</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -5237,7 +5146,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ES114</t>
+          <t>ES120</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -5250,7 +5159,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ES120</t>
+          <t>ES130</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -5263,7 +5172,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ES130</t>
+          <t>ES211</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -5276,7 +5185,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ES211</t>
+          <t>ES212</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -5289,7 +5198,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ES212</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -5302,7 +5211,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ES213</t>
+          <t>ES220</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -5315,7 +5224,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ES220</t>
+          <t>ES230</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -5328,7 +5237,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ES230</t>
+          <t>ES241</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -5341,7 +5250,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ES241</t>
+          <t>ES242</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -5354,7 +5263,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ES242</t>
+          <t>ES243</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -5367,7 +5276,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ES243</t>
+          <t>ES300</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -5380,7 +5289,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ES300</t>
+          <t>ES412</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -5393,7 +5302,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ES412</t>
+          <t>ES413</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -5406,7 +5315,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ES413</t>
+          <t>ES414</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -5419,7 +5328,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ES414</t>
+          <t>ES415</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -5432,7 +5341,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ES415</t>
+          <t>ES416</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -5445,7 +5354,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ES416</t>
+          <t>ES417</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -5458,7 +5367,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ES417</t>
+          <t>ES418</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -5471,7 +5380,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ES418</t>
+          <t>ES419</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -5484,7 +5393,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ES419</t>
+          <t>ES421</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -5497,7 +5406,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ES421</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -5510,7 +5419,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES423</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -5523,7 +5432,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ES423</t>
+          <t>ES424</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -5536,7 +5445,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ES424</t>
+          <t>ES425</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -5549,7 +5458,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ES425</t>
+          <t>ES431</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -5562,7 +5471,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ES431</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -5575,7 +5484,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>ES511</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -5588,7 +5497,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ES511</t>
+          <t>ES512</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -5601,7 +5510,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ES512</t>
+          <t>ES513</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -5614,7 +5523,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ES513</t>
+          <t>ES514</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -5627,7 +5536,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ES514</t>
+          <t>ES521</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -5640,7 +5549,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ES521</t>
+          <t>ES522</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -5653,7 +5562,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ES522</t>
+          <t>ES523</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -5666,7 +5575,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ES523</t>
+          <t>ES532</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -5679,7 +5588,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ES532</t>
+          <t>ES611</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -5692,7 +5601,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ES611</t>
+          <t>ES612</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -5705,7 +5614,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ES612</t>
+          <t>ES613</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -5718,7 +5627,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ES613</t>
+          <t>ES614</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -5731,7 +5640,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ES614</t>
+          <t>ES615</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -5744,7 +5653,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ES615</t>
+          <t>ES616</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -5757,7 +5666,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ES616</t>
+          <t>ES617</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -5770,7 +5679,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ES617</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -5783,26 +5692,13 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ES618</t>
+          <t>ES620</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>ES620</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>1</v>
-      </c>
-      <c r="C54" t="n">
         <v>22000</v>
       </c>
     </row>
@@ -5817,7 +5713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B54"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5861,37 +5757,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>44940000</v>
+        <v>16050000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16050000</v>
+        <v>485576700</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>440636700</v>
+        <v>956170.213</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES112</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5901,7 +5797,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ES112</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5911,7 +5807,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES114</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -5921,7 +5817,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ES114</t>
+          <t>ES120</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -5931,7 +5827,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ES120</t>
+          <t>ES130</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -5941,7 +5837,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ES130</t>
+          <t>ES211</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -5951,7 +5847,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ES211</t>
+          <t>ES212</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -5961,7 +5857,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ES212</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -5971,7 +5867,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ES213</t>
+          <t>ES220</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -5981,7 +5877,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ES220</t>
+          <t>ES230</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -5991,7 +5887,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ES230</t>
+          <t>ES241</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -6001,7 +5897,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ES241</t>
+          <t>ES242</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -6011,7 +5907,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ES242</t>
+          <t>ES243</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -6021,7 +5917,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ES243</t>
+          <t>ES300</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -6031,7 +5927,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ES300</t>
+          <t>ES412</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -6041,7 +5937,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ES412</t>
+          <t>ES413</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -6051,7 +5947,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ES413</t>
+          <t>ES414</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -6061,7 +5957,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ES414</t>
+          <t>ES415</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -6071,7 +5967,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ES415</t>
+          <t>ES416</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -6081,7 +5977,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ES416</t>
+          <t>ES417</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -6091,7 +5987,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ES417</t>
+          <t>ES418</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -6101,7 +5997,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ES418</t>
+          <t>ES419</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -6111,7 +6007,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ES419</t>
+          <t>ES421</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -6121,7 +6017,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ES421</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -6131,7 +6027,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES423</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -6141,7 +6037,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ES423</t>
+          <t>ES424</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -6151,7 +6047,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ES424</t>
+          <t>ES425</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -6161,7 +6057,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ES425</t>
+          <t>ES431</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -6171,7 +6067,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ES431</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -6181,7 +6077,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>ES511</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -6191,7 +6087,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ES511</t>
+          <t>ES512</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -6201,7 +6097,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ES512</t>
+          <t>ES513</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -6211,7 +6107,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ES513</t>
+          <t>ES514</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -6221,7 +6117,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ES514</t>
+          <t>ES521</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -6231,7 +6127,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ES521</t>
+          <t>ES522</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -6241,7 +6137,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ES522</t>
+          <t>ES523</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -6251,7 +6147,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ES523</t>
+          <t>ES532</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -6261,7 +6157,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ES532</t>
+          <t>ES611</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -6271,7 +6167,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ES611</t>
+          <t>ES612</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -6281,7 +6177,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ES612</t>
+          <t>ES613</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -6291,7 +6187,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ES613</t>
+          <t>ES614</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -6301,7 +6197,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ES614</t>
+          <t>ES615</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -6311,7 +6207,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ES615</t>
+          <t>ES616</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -6321,7 +6217,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ES616</t>
+          <t>ES617</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -6331,7 +6227,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ES617</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -6341,20 +6237,10 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ES618</t>
+          <t>ES620</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>956170.213</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>ES620</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
         <v>956170.213</v>
       </c>
     </row>
